--- a/artfynd/A 3920-2025 artfynd.xlsx
+++ b/artfynd/A 3920-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>75026143</v>
       </c>
       <c r="B2" t="n">
-        <v>101141</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103128</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565334.3286731552</v>
+        <v>565334</v>
       </c>
       <c r="R2" t="n">
-        <v>6277448.000674512</v>
+        <v>6277448</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1997-05-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1997-05-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 3920-2025 artfynd.xlsx
+++ b/artfynd/A 3920-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75026143</v>
       </c>
       <c r="B2" t="n">
-        <v>103128</v>
+        <v>103134</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 3920-2025 artfynd.xlsx
+++ b/artfynd/A 3920-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75026143</v>
       </c>
       <c r="B2" t="n">
-        <v>103134</v>
+        <v>103136</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 3920-2025 artfynd.xlsx
+++ b/artfynd/A 3920-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75026143</v>
       </c>
       <c r="B2" t="n">
-        <v>103136</v>
+        <v>103163</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 3920-2025 artfynd.xlsx
+++ b/artfynd/A 3920-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75026143</v>
       </c>
       <c r="B2" t="n">
-        <v>103163</v>
+        <v>103169</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 3920-2025 artfynd.xlsx
+++ b/artfynd/A 3920-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75026143</v>
       </c>
       <c r="B2" t="n">
-        <v>103169</v>
+        <v>103176</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 3920-2025 artfynd.xlsx
+++ b/artfynd/A 3920-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75026143</v>
       </c>
       <c r="B2" t="n">
-        <v>103176</v>
+        <v>103180</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 3920-2025 artfynd.xlsx
+++ b/artfynd/A 3920-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75026143</v>
       </c>
       <c r="B2" t="n">
-        <v>103180</v>
+        <v>103187</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 3920-2025 artfynd.xlsx
+++ b/artfynd/A 3920-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75026143</v>
       </c>
       <c r="B2" t="n">
-        <v>103190</v>
+        <v>103195</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 3920-2025 artfynd.xlsx
+++ b/artfynd/A 3920-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75026143</v>
       </c>
       <c r="B2" t="n">
-        <v>103195</v>
+        <v>103203</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 3920-2025 artfynd.xlsx
+++ b/artfynd/A 3920-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75026143</v>
       </c>
       <c r="B2" t="n">
-        <v>103203</v>
+        <v>103213</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 3920-2025 artfynd.xlsx
+++ b/artfynd/A 3920-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>75026143</v>
+        <v>75026141</v>
       </c>
       <c r="B2" t="n">
-        <v>103213</v>
+        <v>103703</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -740,17 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1997-05-19</t>
+          <t>1999-05-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1997-05-19</t>
+          <t>1999-05-30</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 4G5d 3809. SOM: Viola uliginosa. LEG: Ronny Gustavsson. KOM: 800-tal ex</t>
+          <t>Smålands flora 2007: KOO: 4G5d 3809. SOM: Viola uliginosa. LEG: Ronny Gustavsson. KOM: 600-tal ex</t>
         </is>
       </c>
       <c r="AD2" t="b">
